--- a/02_DIA_inicio_2026_analisis_assets/rbd_25173_esc-basica-municipal-risopatron_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_25173_esc-basica-municipal-risopatron_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C59AE531-3AB6-4C05-BB73-282F104186C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB76FC6-CE19-4503-85F8-76F792478402}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52A9C545-A7CA-43EE-B230-E338BD939E65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C3DE868-F584-4FC7-B97D-6FE2760BC599}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D155EDB-2D7A-4971-91C6-974587D81A13}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF265645-0C9F-4465-B810-55CE7B818569}"/>
 </file>